--- a/technical_assessment_by_job/questions/sql_questions.xlsx
+++ b/technical_assessment_by_job/questions/sql_questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_openai_ws\technical_assessment_by_job\questions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_openai\codex_projects\technical_assessment_by_job\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5053482D-8806-462A-AC21-8F49E5F909B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053480B9-8296-4CF2-A18E-FB9DA20E0B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2D37F685-2502-4A38-84D9-569A1400D5DB}"/>
   </bookViews>
@@ -35,10 +35,1148 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="375">
+  <si>
+    <t>What is SQL?</t>
+  </si>
+  <si>
+    <t>SQL stands for Structured Query Language. It is the standard language for relational database management systems, used to communicate with a database and perform tasks such as retrieval, update, and deletion of data.</t>
+  </si>
+  <si>
+    <t>What is a Database?</t>
+  </si>
+  <si>
+    <t>A database is a structured collection of data that is organized so that it can be easily accessed, managed, and updated.</t>
+  </si>
+  <si>
+    <t>What is a DBMS?</t>
+  </si>
+  <si>
+    <t>DBMS (Database Management System) is software that interacts with end users, applications, and the database itself to capture and analyze data.</t>
+  </si>
+  <si>
+    <t>What is RDBMS?</t>
+  </si>
+  <si>
+    <t>Relational Database Management System (RDBMS) is a database management system based on the relational model. Data is stored in tables, and the relationships between the data are also stored in tables.</t>
+  </si>
+  <si>
+    <t>What are the different types of SQL commands?</t>
+  </si>
+  <si>
+    <t>DDL (Data Definition Language), DML (Data Manipulation Language), DCL (Data Control Language), TCL (Transaction Control Language), and DQL (Data Query Language).</t>
+  </si>
+  <si>
+    <t>What is a Table and Field?</t>
+  </si>
+  <si>
+    <t>A table is a collection of related data entries consisting of columns and rows. A field is a column in a table that maintains specific information about every record in the table.</t>
+  </si>
+  <si>
+    <t>What is a Primary Key?</t>
+  </si>
+  <si>
+    <t>A Primary Key is a unique identifier for a record in a table. It cannot contain NULL values and must be unique across the table.</t>
+  </si>
+  <si>
+    <t>What is a Foreign Key?</t>
+  </si>
+  <si>
+    <t>A Foreign Key is a column or a group of columns in a relational database table that provides a link between data in two tables. It acts as a cross-reference between tables.</t>
+  </si>
+  <si>
+    <t>What is a Unique Key?</t>
+  </si>
+  <si>
+    <t>A Unique Key uniquely identifies each record in a database table. Unlike a Primary Key, it can accept one NULL value per column.</t>
+  </si>
+  <si>
+    <t>What is a Join?</t>
+  </si>
+  <si>
+    <t>A JOIN clause is used to combine rows from two or more tables, based on a related column between them.</t>
+  </si>
+  <si>
+    <t>What are the types of Joins?</t>
+  </si>
+  <si>
+    <t>Inner Join, Left (Outer) Join, Right (Outer) Join, and Full (Outer) Join.</t>
+  </si>
+  <si>
+    <t>What is an Inner Join?</t>
+  </si>
+  <si>
+    <t>The INNER JOIN keyword selects records that have matching values in both tables.</t>
+  </si>
+  <si>
+    <t>What is a Self Join?</t>
+  </si>
+  <si>
+    <t>A self join is a regular join, but the table is joined with itself.</t>
+  </si>
+  <si>
+    <t>What is a Cross Join?</t>
+  </si>
+  <si>
+    <t>A Cross Join produces a Cartesian product of the two tables (every row from table A paired with every row from table B).</t>
+  </si>
+  <si>
+    <t>What is a Constraint?</t>
+  </si>
+  <si>
+    <t>Constraints are rules used to limit the type of data that can go into a table. Examples: NOT NULL, UNIQUE, PRIMARY KEY, FOREIGN KEY, CHECK, DEFAULT.</t>
+  </si>
+  <si>
+    <t>What is the difference between BETWEEN and IN operators?</t>
+  </si>
+  <si>
+    <t>BETWEEN is used to retrieve values within a range, while IN is used to check for values that match any value in a specified list.</t>
+  </si>
+  <si>
+    <t>What is a View?</t>
+  </si>
+  <si>
+    <t>A view is a virtual table based on the result-set of an SQL statement. It does not store data itself.</t>
+  </si>
+  <si>
+    <t>What is an Index?</t>
+  </si>
+  <si>
+    <t>An index is a performance tuning method that allows faster retrieval of records from a table.</t>
+  </si>
+  <si>
+    <t>Difference between DELETE and TRUNCATE?</t>
+  </si>
+  <si>
+    <t>DELETE is a DML command used to remove specific rows (can be rolled back). TRUNCATE is a DDL command that removes all rows (cannot be rolled back in most systems) and is faster.</t>
+  </si>
+  <si>
+    <t>Difference between DROP and TRUNCATE?</t>
+  </si>
+  <si>
+    <t>DROP removes the entire table structure and data. TRUNCATE removes only the data, keeping the table structure intact.</t>
+  </si>
+  <si>
+    <t>What is Aggregate Function?</t>
+  </si>
+  <si>
+    <t>An aggregate function performs a calculation on a set of values and returns a single value. Examples: AVG(), COUNT(), MAX(), MIN(), SUM().</t>
+  </si>
+  <si>
+    <t>What is the GROUP BY clause?</t>
+  </si>
+  <si>
+    <t>The GROUP BY statement groups rows that have the same values into summary rows, like 'find the number of customers in each country'.</t>
+  </si>
+  <si>
+    <t>What is the HAVING clause?</t>
+  </si>
+  <si>
+    <t>The HAVING clause was added to SQL because the WHERE keyword could not be used with aggregate functions. It filters groups.</t>
+  </si>
+  <si>
+    <t>What is a Subquery?</t>
+  </si>
+  <si>
+    <t>A Subquery or Inner query or a Nested query is a query within another SQL query.</t>
+  </si>
+  <si>
+    <t>What are the types of Subqueries?</t>
+  </si>
+  <si>
+    <t>Single-row subquery, Multi-row subquery, and Correlated subquery.</t>
+  </si>
+  <si>
+    <t>What is a Correlated Subquery?</t>
+  </si>
+  <si>
+    <t>A correlated subquery is a subquery that uses values from the outer query. It is evaluated once for each row processed by the outer query.</t>
+  </si>
+  <si>
+    <t>What is the difference between UNION and UNION ALL?</t>
+  </si>
+  <si>
+    <t>UNION selects only distinct values. UNION ALL selects all values, including duplicates.</t>
+  </si>
+  <si>
+    <t>What is ACID property?</t>
+  </si>
+  <si>
+    <t>ACID stands for Atomicity, Consistency, Isolation, and Durability. These properties ensure that database transactions are processed reliably.</t>
+  </si>
+  <si>
+    <t>What is a Trigger?</t>
+  </si>
+  <si>
+    <t>A trigger is a stored procedure that automatically runs when an event (like INSERT, UPDATE, or DELETE) occurs in the database server.</t>
+  </si>
+  <si>
+    <t>What is a Stored Procedure?</t>
+  </si>
+  <si>
+    <t>A stored procedure is a prepared SQL code that you can save, so the code can be reused over and over again.</t>
+  </si>
+  <si>
+    <t>Difference between Function and Stored Procedure?</t>
+  </si>
+  <si>
+    <t>Functions must return a value and cannot change the database state. Stored Procedures may or may not return a value and can modify the database.</t>
+  </si>
+  <si>
+    <t>What is Normalization?</t>
+  </si>
+  <si>
+    <t>Normalization is the process of organizing data in a database to avoid data redundancy and dependency.</t>
+  </si>
+  <si>
+    <t>What are the types of Normalization?</t>
+  </si>
+  <si>
+    <t>1NF, 2NF, 3NF, BCNF, etc.</t>
+  </si>
+  <si>
+    <t>What is Denormalization?</t>
+  </si>
+  <si>
+    <t>Denormalization is a database optimization technique in which we add redundant data to one or more tables to avoid costly joins.</t>
+  </si>
+  <si>
+    <t>What is a Cursor?</t>
+  </si>
+  <si>
+    <t>A cursor is a database object used to retrieve data from a result set one row at a time.</t>
+  </si>
+  <si>
+    <t>What are the different types of Cursors?</t>
+  </si>
+  <si>
+    <t>Implicit and Explicit cursors.</t>
+  </si>
+  <si>
+    <t>What is the difference between NVL, IFNULL, and COALESCE?</t>
+  </si>
+  <si>
+    <t>They are used to handle NULL values. NVL (Oracle), IFNULL (MySQL), and COALESCE (Standard SQL) return the first non-null value in a list.</t>
+  </si>
+  <si>
+    <t>What is a Data Warehouse?</t>
+  </si>
+  <si>
+    <t>A data warehouse is a central repository of information that can be analyzed to make better-informed decisions.</t>
+  </si>
+  <si>
+    <t>What is the difference between OLTP and OLAP?</t>
+  </si>
+  <si>
+    <t>OLTP (Online Transactional Processing) manages transaction-oriented applications. OLAP (Online Analytical Processing) handles multi-dimensional queries for data analysis.</t>
+  </si>
+  <si>
+    <t>What is Collation?</t>
+  </si>
+  <si>
+    <t>Collation is a set of rules that determine how data is sorted and compared.</t>
+  </si>
+  <si>
+    <t>What is a Cross Apply vs Outer Apply?</t>
+  </si>
+  <si>
+    <t>Apply operators are used to join a table to a table-valued function. Cross Apply is similar to Inner Join, while Outer Apply is similar to Left Outer Join.</t>
+  </si>
+  <si>
+    <t>What is a Recursive CTE?</t>
+  </si>
+  <si>
+    <t>A Common Table Expression (CTE) that references itself. It's useful for querying hierarchical data like organizational charts.</t>
+  </si>
+  <si>
+    <t>Explain the difference between Rank(), Dense_Rank(), and Row_Number().</t>
+  </si>
+  <si>
+    <t>Row_Number() gives a unique incrementing integer. Rank() leaves gaps in sequence after a tie. Dense_Rank() leaves no gaps after a tie.</t>
+  </si>
+  <si>
+    <t>What is Sharding?</t>
+  </si>
+  <si>
+    <t>Sharding is a type of database partitioning that separates very large databases into smaller, faster, more easily managed parts called data shards.</t>
+  </si>
+  <si>
+    <t>What is Database Partitioning?</t>
+  </si>
+  <si>
+    <t>The process of dividing a large database into smaller, more manageable logical units called partitions.</t>
+  </si>
+  <si>
+    <t>What is an Execution Plan?</t>
+  </si>
+  <si>
+    <t>A visual or textual description of the steps the database engine takes to execute a query.</t>
+  </si>
+  <si>
+    <t>What is Deadlock?</t>
+  </si>
+  <si>
+    <t>A situation where two or more transactions are waiting for each other to release locks, causing a permanent stall.</t>
+  </si>
+  <si>
+    <t>How to prevent Deadlock?</t>
+  </si>
+  <si>
+    <t>Keep transactions short, access objects in the same order, and use appropriate isolation levels.</t>
+  </si>
+  <si>
+    <t>What is the difference between Clustered and Non-Clustered Index?</t>
+  </si>
+  <si>
+    <t>A Clustered index defines the physical order of data in the table (one per table). A Non-Clustered index stores a separate structure with pointers to the data (multiple per table).</t>
+  </si>
+  <si>
+    <t>What is the 'Magic Tables' in SQL Server?</t>
+  </si>
+  <si>
+    <t>Inserted and Deleted tables used within triggers to access the data being affected by the transaction.</t>
+  </si>
+  <si>
+    <t>What is Data Integrity?</t>
+  </si>
+  <si>
+    <t>Data integrity refers to the accuracy, consistency, and reliability of data stored in a database.</t>
+  </si>
+  <si>
+    <t>What is a Cardinality?</t>
+  </si>
+  <si>
+    <t>It refers to the uniqueness of data values contained in a particular column (high cardinality means many unique values).</t>
+  </si>
+  <si>
+    <t>What is NoSQL?</t>
+  </si>
+  <si>
+    <t>NoSQL (Not Only SQL) databases are non-tabular and store data differently than relational tables (Document, Key-Value, Graph, Wide-column).</t>
+  </si>
+  <si>
+    <t>What is the difference between SQL and NoSQL?</t>
+  </si>
+  <si>
+    <t>SQL is relational, structured, and scales vertically. NoSQL is non-relational, distributed, and scales horizontally.</t>
+  </si>
+  <si>
+    <t>What is Database Mirroring?</t>
+  </si>
+  <si>
+    <t>A solution for increasing database availability by maintaining a copy of a database on a different server.</t>
+  </si>
+  <si>
+    <t>What is ETL?</t>
+  </si>
+  <si>
+    <t>Extract, Transform, and Load—the three steps used to integrate data from multiple sources into a data warehouse.</t>
+  </si>
+  <si>
+    <t>What is the difference between Static and Dynamic SQL?</t>
+  </si>
+  <si>
+    <t>Static SQL is fixed and compiled at compile time. Dynamic SQL is constructed and executed at runtime.</t>
+  </si>
+  <si>
+    <t>Explain 3-Tier Architecture.</t>
+  </si>
+  <si>
+    <t>Consists of the Presentation Layer (UI), Application Layer (Logic), and Database Layer (Data).</t>
+  </si>
+  <si>
+    <t>What is a composite primary key?</t>
+  </si>
+  <si>
+    <t>A primary key made up of two or more columns to uniquely identify a row.</t>
+  </si>
+  <si>
+    <t>What is a Surrogate Key?</t>
+  </si>
+  <si>
+    <t>A system-generated unique identifier (like an Identity column) that has no business meaning.</t>
+  </si>
+  <si>
+    <t>What is a Natural Key?</t>
+  </si>
+  <si>
+    <t>A key that has a logical relationship with the attributes within the row (e.g., SSN).</t>
+  </si>
+  <si>
+    <t>What is a schema?</t>
+  </si>
+  <si>
+    <t>A logical container or structure that defines the organization of data in a database.</t>
+  </si>
+  <si>
+    <t>What is a window function?</t>
+  </si>
+  <si>
+    <t>A function that performs a calculation across a set of table rows that are somehow related to the current row (e.g., OVER clause).</t>
+  </si>
+  <si>
+    <t>Difference between Lead and Lag functions?</t>
+  </si>
+  <si>
+    <t>Lag() accesses data from a previous row, and Lead() accesses data from a subsequent row.</t>
+  </si>
+  <si>
+    <t>Explain the CASE statement.</t>
+  </si>
+  <si>
+    <t>SQL's way of handling if-then-else logic within a query.</t>
+  </si>
+  <si>
+    <t>What is the use of the MERGE statement?</t>
+  </si>
+  <si>
+    <t>It allows you to perform INSERT, UPDATE, and DELETE operations in a single statement based on differences between a source and target table.</t>
+  </si>
+  <si>
+    <t>Explain the concept of 'Dirty Read'.</t>
+  </si>
+  <si>
+    <t>When a transaction reads data that has been modified by another transaction but not yet committed.</t>
+  </si>
+  <si>
+    <t>What is 'Phantom Read'?</t>
+  </si>
+  <si>
+    <t>When a transaction re-queries a range of rows and finds that a row has been added or removed by another committed transaction.</t>
+  </si>
+  <si>
+    <t>What are Isolation Levels?</t>
+  </si>
+  <si>
+    <t>The levels that define the degree to which one transaction must be isolated from resource or data modifications made by other transactions (Read Uncommitted, Read Committed, Repeatable Read, Serializable).</t>
+  </si>
+  <si>
+    <t>What is a materialised view?</t>
+  </si>
+  <si>
+    <t>A view whose result-set is physically stored in the database, allowing for faster access at the cost of being slightly out of date or requiring refresh.</t>
+  </si>
+  <si>
+    <t>What is the difference between HASH and B-Tree indexes?</t>
+  </si>
+  <si>
+    <t>B-Tree is good for range queries; Hash is extremely fast for equality (=) comparisons but cannot do ranges.</t>
+  </si>
+  <si>
+    <t>What is Cursor Loss?</t>
+  </si>
+  <si>
+    <t>A situation where a cursor is closed before the completion of the required operation.</t>
+  </si>
+  <si>
+    <t>Explain 'Tuning' a query.</t>
+  </si>
+  <si>
+    <t>The process of analyzing and modifying a query to reduce resource consumption and increase execution speed.</t>
+  </si>
+  <si>
+    <t>What is 'SARGable'?</t>
+  </si>
+  <si>
+    <t>Search ARGumentable; a query is SARGable if the database engine can take advantage of an index to speed up the execution.</t>
+  </si>
+  <si>
+    <t>What is a 'Full Table Scan'?</t>
+  </si>
+  <si>
+    <t>When the database has to read every single row in a table to find the requested data because no suitable index is available.</t>
+  </si>
+  <si>
+    <t>What is 'Referential Integrity'?</t>
+  </si>
+  <si>
+    <t>A property of data stating that all its references are valid (i.e., every foreign key value exists as a primary key in the related table).</t>
+  </si>
+  <si>
+    <t>What is the 'Self-Healing' database?</t>
+  </si>
+  <si>
+    <t>A modern cloud database concept where the system automatically detects and fixes issues like corruption or performance bottlenecks.</t>
+  </si>
+  <si>
+    <t>Explain the 'EXISTS' operator.</t>
+  </si>
+  <si>
+    <t>It is used to test for the existence of any record in a subquery; it returns true if the subquery returns one or more records.</t>
+  </si>
+  <si>
+    <t>What is 'Interleaving' in databases?</t>
+  </si>
+  <si>
+    <t>A method to improve performance by placing related data from different tables physically close to each other on the disk.</t>
+  </si>
+  <si>
+    <t>What is 'Query Refactoring'?</t>
+  </si>
+  <si>
+    <t>Restructuring an existing SQL query to improve performance or readability without changing its original result.</t>
+  </si>
+  <si>
+    <t>What is 'Vertical Scaling'?</t>
+  </si>
+  <si>
+    <t>Increasing the capacity of a single server (more CPU, RAM).</t>
+  </si>
+  <si>
+    <t>What is 'Horizontal Scaling'?</t>
+  </si>
+  <si>
+    <t>Adding more servers to the database cluster (Sharding).</t>
+  </si>
+  <si>
+    <t>What is 'Cold Backup' vs 'Hot Backup'?</t>
+  </si>
+  <si>
+    <t>Cold backup happens while the database is offline. Hot backup happens while it is online and running.</t>
+  </si>
+  <si>
+    <t>What is a 'Database Cluster'?</t>
+  </si>
+  <si>
+    <t>A group of database servers working together as a single system to provide high availability and load balancing.</t>
+  </si>
+  <si>
+    <t>What is 'Object-Relational Mapping' (ORM)?</t>
+  </si>
+  <si>
+    <t>A technique for converting data between incompatible type systems in object-oriented programming languages and relational databases (e.g., Hibernate).</t>
+  </si>
+  <si>
+    <t>What is 'SQL Injection'?</t>
+  </si>
+  <si>
+    <t>A security vulnerability where an attacker can interfere with the queries that an application makes to its database.</t>
+  </si>
+  <si>
+    <t>How to prevent SQL Injection?</t>
+  </si>
+  <si>
+    <t>Use prepared statements (parameterized queries) and input validation.</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>What is SQL and what is its use?</t>
+  </si>
+  <si>
+    <t>SQL (Structured Query Language) is a standard programming language specifically designed for managing and manipulating data held in a relational database management system (RDBMS). It is used to query, insert, update, and delete database records.</t>
+  </si>
+  <si>
+    <t>What is a database?</t>
+  </si>
+  <si>
+    <t>A database is an organized collection of structured information, or data, typically stored electronically in a computer system. A database is usually controlled by a database management system (DBMS).</t>
+  </si>
+  <si>
+    <t>What is a table in SQL?</t>
+  </si>
+  <si>
+    <t>A table is a collection of related data entries and it consists of columns and rows. It is the basic unit of storage in a relational database.</t>
+  </si>
+  <si>
+    <t>What are rows and columns in a table?</t>
+  </si>
+  <si>
+    <t>A column (field) is a vertical entity in a table that contains all information associated with a specific field in a table. A row (record/tuple) is a horizontal entity in a table that represents a single, implicitly structured data item in a table.</t>
+  </si>
+  <si>
+    <t>What is the difference between DELETE, TRUNCATE, and DROP commands?</t>
+  </si>
+  <si>
+    <t>DELETE is a DML command used to remove specific rows (can be rolled back). TRUNCATE is a DDL command that removes all rows from a table (faster, resets identity). DROP is a DDL command that removes the entire table structure and data from the database.</t>
+  </si>
+  <si>
+    <t>How do you retrieve all the records from a table?</t>
+  </si>
+  <si>
+    <t>By using the SELECT statement with an asterisk: 'SELECT * FROM table_name;'</t>
+  </si>
+  <si>
+    <t>What is a primary key?</t>
+  </si>
+  <si>
+    <t>A primary key is a column or a set of columns that uniquely identifies each row in a table. It must contain unique values and cannot contain NULL values.</t>
+  </si>
+  <si>
+    <t>What is a foreign key?</t>
+  </si>
+  <si>
+    <t>A foreign key is a field (or collection of fields) in one table, that refers to the PRIMARY KEY in another table. It is used to link two tables together.</t>
+  </si>
+  <si>
+    <t>What is a unique constraint?</t>
+  </si>
+  <si>
+    <t>A unique constraint ensures that all values in a column are different. Unlike a primary key, a unique constraint can accept one NULL value (in most SQL dialects).</t>
+  </si>
+  <si>
+    <t>What is an index in SQL?</t>
+  </si>
+  <si>
+    <t>An index is a performance tuning method that allows for faster retrieval of records from a table. It creates an entry for each value and it makes it faster to retrieve data.</t>
+  </si>
+  <si>
+    <t>What is a NULL value?</t>
+  </si>
+  <si>
+    <t>A NULL value represents a missing, unknown, or inapplicable value. It is different from zero or an empty string, which are actual values.</t>
+  </si>
+  <si>
+    <t>What is the purpose of the WHERE clause?</t>
+  </si>
+  <si>
+    <t>The WHERE clause is used to filter records. It is used to extract only those records that fulfill a specified condition.</t>
+  </si>
+  <si>
+    <t>What is the SELECT statement used for?</t>
+  </si>
+  <si>
+    <t>The SELECT statement is used to select data from a database. The data returned is stored in a result table, called the result-set.</t>
+  </si>
+  <si>
+    <t>What are aggregate functions in SQL?</t>
+  </si>
+  <si>
+    <t>Aggregate functions perform a calculation on a set of values and return a single value. Examples include COUNT(), SUM(), AVG(), MIN(), and MAX().</t>
+  </si>
+  <si>
+    <t>What is the GROUP BY clause used for?</t>
+  </si>
+  <si>
+    <t>What is the ORDER BY clause?</t>
+  </si>
+  <si>
+    <t>The ORDER BY keyword is used to sort the result-set in ascending (ASC) or descending (DESC) order.</t>
+  </si>
+  <si>
+    <t>What is the difference between INNER JOIN and OUTER JOIN?</t>
+  </si>
+  <si>
+    <t>INNER JOIN returns records that have matching values in both tables. OUTER JOIN returns records when there is a match in either the left or right table (or both).</t>
+  </si>
+  <si>
+    <t>What is a subquery?</t>
+  </si>
+  <si>
+    <t>A subquery is a query nested inside another query (the outer query). It can be used in SELECT, INSERT, UPDATE, or DELETE statements.</t>
+  </si>
+  <si>
+    <t>What is the HAVING clause in SQL?</t>
+  </si>
+  <si>
+    <t>The HAVING clause was added to SQL because the WHERE keyword could not be used with aggregate functions. It is used to filter groups created by GROUP BY.</t>
+  </si>
+  <si>
+    <t>What is a Cartesian Join?</t>
+  </si>
+  <si>
+    <t>Also known as a CROSS JOIN, it returns the Cartesian product of the sets of rows from the joined tables (every row from table A joined with every row from table B).</t>
+  </si>
+  <si>
+    <t>What is a self join in SQL?</t>
+  </si>
+  <si>
+    <t>What is the DISTINCT keyword used for?</t>
+  </si>
+  <si>
+    <t>The SELECT DISTINCT statement is used to return only distinct (different) values from a specific column.</t>
+  </si>
+  <si>
+    <t>How do you update data in SQL using the UPDATE statement?</t>
+  </si>
+  <si>
+    <t>By using the syntax: 'UPDATE table_name SET column1 = value1 WHERE condition;'</t>
+  </si>
+  <si>
+    <t>What is the INSERT INTO statement?</t>
+  </si>
+  <si>
+    <t>It is used to insert new records in a table.</t>
+  </si>
+  <si>
+    <t>How do you delete records from a table?</t>
+  </si>
+  <si>
+    <t>By using the DELETE statement: 'DELETE FROM table_name WHERE condition;'</t>
+  </si>
+  <si>
+    <t>What is the purpose of the LIMIT clause?</t>
+  </si>
+  <si>
+    <t>The LIMIT clause is used to specify the number of records to return. Useful on large tables for pagination.</t>
+  </si>
+  <si>
+    <t>Differences between CHAR and VARCHAR data types?</t>
+  </si>
+  <si>
+    <t>CHAR is a fixed-length character string. VARCHAR is a variable-length character string.</t>
+  </si>
+  <si>
+    <t>What is the BETWEEN operator used for?</t>
+  </si>
+  <si>
+    <t>The BETWEEN operator selects values within a given range. The values can be numbers, text, or dates.</t>
+  </si>
+  <si>
+    <t>What is the difference between IN and EXISTS?</t>
+  </si>
+  <si>
+    <t>IN is used to match a column's value against a list of literal values or a subquery result. EXISTS is used to check for the existence of any record in a subquery (often more efficient for large datasets).</t>
+  </si>
+  <si>
+    <t>What are SQL constraints?</t>
+  </si>
+  <si>
+    <t>Constraints are rules used to limit the type of data that can go into a table. Types include NOT NULL, UNIQUE, PRIMARY KEY, FOREIGN KEY, CHECK, and DEFAULT.</t>
+  </si>
+  <si>
+    <t>What is the ALTER command used for?</t>
+  </si>
+  <si>
+    <t>The ALTER TABLE statement is used to add, delete, or modify columns in an existing table.</t>
+  </si>
+  <si>
+    <t>What are views in SQL?</t>
+  </si>
+  <si>
+    <t>A view is a virtual table based on the result-set of an SQL statement. It allows users to simplify complex queries and restrict access to data.</t>
+  </si>
+  <si>
+    <t>What is a schema in SQL?</t>
+  </si>
+  <si>
+    <t>A schema is a collection of database objects, including tables, views, indexes, and procedures, associated with a particular database user or application.</t>
+  </si>
+  <si>
+    <t>What is the CASE statement in SQL?</t>
+  </si>
+  <si>
+    <t>The CASE statement goes through conditions and returns a value when the first condition is met (like an if-then-else statement).</t>
+  </si>
+  <si>
+    <t>Difference between UNION and UNION ALL?</t>
+  </si>
+  <si>
+    <t>UNION selects only distinct values by default. UNION ALL selects all values, including duplicates.</t>
+  </si>
+  <si>
+    <t>What is normalization?</t>
+  </si>
+  <si>
+    <t>Normalization is the process of organizing data in a database to reduce redundancy and improve data integrity (1NF, 2NF, 3NF).</t>
+  </si>
+  <si>
+    <t>What is denormalization?</t>
+  </si>
+  <si>
+    <t>Denormalization is the process of adding redundant data to a database to improve read performance (reducing the number of joins).</t>
+  </si>
+  <si>
+    <t>How do you find duplicate records in a table?</t>
+  </si>
+  <si>
+    <t>By using GROUP BY and HAVING COUNT(*) &gt; 1 on the columns that should be unique.</t>
+  </si>
+  <si>
+    <t>What is the COALESCE function?</t>
+  </si>
+  <si>
+    <t>COALESCE returns the first non-null value in a list of arguments.</t>
+  </si>
+  <si>
+    <t>What is ROW_NUMBER()?</t>
+  </si>
+  <si>
+    <t>A window function that assigns a unique sequential integer to rows within a partition of a result set.</t>
+  </si>
+  <si>
+    <t>How do you find the second highest salary?</t>
+  </si>
+  <si>
+    <t>Example: 'SELECT MAX(salary) FROM employees WHERE salary &lt; (SELECT MAX(salary) FROM employees);'</t>
+  </si>
+  <si>
+    <t>What is SQL injection?</t>
+  </si>
+  <si>
+    <t>A type of vulnerability where an attacker can interfere with queries by inserting malicious SQL code into input fields.</t>
+  </si>
+  <si>
+    <t>What is a TRANSACTION?</t>
+  </si>
+  <si>
+    <t>A transaction is a single unit of work. If it succeeds, all changes are committed; if it fails, it can be rolled back to its original state.</t>
+  </si>
+  <si>
+    <t>What are ACID properties?</t>
+  </si>
+  <si>
+    <t>Atomicity, Consistency, Isolation, and Durability - properties that ensure reliable database transactions.</t>
+  </si>
+  <si>
+    <t>What is the RANK() function?</t>
+  </si>
+  <si>
+    <t>A window function that assigns a rank to each row within a partition. If there are ties, ranks are skipped (e.g., 1, 2, 2, 4).</t>
+  </si>
+  <si>
+    <t>What is a TRIGGER?</t>
+  </si>
+  <si>
+    <t>A trigger is a set of SQL statements that automatically execute or 'fire' in response to certain events on a particular table or view (INSERT, UPDATE, DELETE).</t>
+  </si>
+  <si>
+    <t>What is a stored procedure?</t>
+  </si>
+  <si>
+    <t>A prepared SQL code that you can save and reuse. It can accept parameters and return multiple values.</t>
+  </si>
+  <si>
+    <t>How do you implement pagination?</t>
+  </si>
+  <si>
+    <t>Usually by combining the LIMIT and OFFSET clauses (or equivalent syntax like TOP/ROW_NUMBER depending on the DB).</t>
+  </si>
+  <si>
+    <t>What is the execution order of a SELECT statement?</t>
+  </si>
+  <si>
+    <t>FROM/JOIN -&gt; WHERE -&gt; GROUP BY -&gt; HAVING -&gt; SELECT -&gt; DISTINCT -&gt; ORDER BY -&gt; LIMIT/OFFSET.</t>
+  </si>
+  <si>
+    <t>What is a Common Table Expression (CTE)?</t>
+  </si>
+  <si>
+    <t>A temporary result set that you can reference within another SELECT, INSERT, UPDATE, or DELETE statement. Defined using the WITH clause.</t>
+  </si>
+  <si>
+    <t>Difference between CTE and derived table?</t>
+  </si>
+  <si>
+    <t>CTEs are more readable, can be recursive, and can be referenced multiple times in the same query. Derived tables are defined in the FROM clause and are less flexible.</t>
+  </si>
+  <si>
+    <t>What are window functions?</t>
+  </si>
+  <si>
+    <t>Functions that perform calculations across a set of table rows that are related to the current row (e.g., SUM() OVER(), RANK()).</t>
+  </si>
+  <si>
+    <t>What is the OVER() clause used for?</t>
+  </si>
+  <si>
+    <t>The OVER clause defines the window or user-specified set of rows within a query result set on which a window function operates.</t>
+  </si>
+  <si>
+    <t>Difference between clustered and non-clustered indexes?</t>
+  </si>
+  <si>
+    <t>Clustered index determines the physical order of data in the table (1 per table). Non-clustered index is a separate structure from the data rows (multiple per table).</t>
+  </si>
+  <si>
+    <t>What is a composite index?</t>
+  </si>
+  <si>
+    <t>An index created on two or more columns of a table.</t>
+  </si>
+  <si>
+    <t>What is index fragmentation?</t>
+  </si>
+  <si>
+    <t>Fragmentation occurs when indexes have pages in which the logical ordering does not match the physical ordering in the data file.</t>
+  </si>
+  <si>
+    <t>What is SARGability?</t>
+  </si>
+  <si>
+    <t>Search ARGumentable; a query is SARGable if the SQL engine can take advantage of an index to speed up the execution.</t>
+  </si>
+  <si>
+    <t>What are isolation levels?</t>
+  </si>
+  <si>
+    <t>Levels that define the degree to which one transaction must be isolated from resource or data modifications made by other transactions (e.g., Read Committed, Serializable).</t>
+  </si>
+  <si>
+    <t>What is a deadlock?</t>
+  </si>
+  <si>
+    <t>A situation where two or more processes are each waiting for the other to release a lock, leading to a standstill.</t>
+  </si>
+  <si>
+    <t>What is dynamic SQL?</t>
+  </si>
+  <si>
+    <t>SQL code that is generated and executed at runtime, often used for building flexible queries based on user input.</t>
+  </si>
+  <si>
+    <t>What is a query execution plan?</t>
+  </si>
+  <si>
+    <t>The set of steps that the database engine uses to access data and generate results for a query.</t>
+  </si>
+  <si>
+    <t>Difference between estimated and actual execution plan?</t>
+  </si>
+  <si>
+    <t>Estimated plan is generated based on statistics without running the query. Actual plan is generated by running the query and reflects real resource usage.</t>
+  </si>
+  <si>
+    <t>What is tempdb?</t>
+  </si>
+  <si>
+    <t>A global resource in SQL Server used to store temporary objects (temporary tables, table variables, intermediate result sets).</t>
+  </si>
+  <si>
+    <t>What is partitioning?</t>
+  </si>
+  <si>
+    <t>Dividing a large table or index into smaller, more manageable pieces called partitions, while still appearing as a single table.</t>
+  </si>
+  <si>
+    <t>What is data skew?</t>
+  </si>
+  <si>
+    <t>When data is not evenly distributed across partitions or values, leading to some processing nodes working harder than others.</t>
+  </si>
+  <si>
+    <t>Difference between heap and clustered table?</t>
+  </si>
+  <si>
+    <t>A heap is a table without a clustered index. Data is stored in no particular order. A clustered table has a primary key or clustered index that dictates storage order.</t>
+  </si>
+  <si>
+    <t>What is the CROSS APPLY vs OUTER APPLY?</t>
+  </si>
+  <si>
+    <t>Used to join a table to a table-valued function. CROSS APPLY returns only matches (like Inner Join). OUTER APPLY returns all rows from the left table (like Left Join).</t>
+  </si>
+  <si>
+    <t>What is the GROUP_CONCAT() function?</t>
+  </si>
+  <si>
+    <t>A MySQL function that returns a string result with the concatenated non-NULL values from a group.</t>
+  </si>
+  <si>
+    <t>What is a temporary table?</t>
+  </si>
+  <si>
+    <t>A table that exists only during the duration of a session or transaction. Used to store intermediate results.</t>
+  </si>
+  <si>
+    <t>What is the difference between UNION and INTERSECT?</t>
+  </si>
+  <si>
+    <t>UNION combines result sets from two queries (all rows). INTERSECT returns only the rows that are present in both result sets.</t>
+  </si>
+  <si>
+    <t>What is the DENSE_RANK() function?</t>
+  </si>
+  <si>
+    <t>Similar to RANK(), but assigns consecutive ranks without gaps if there are ties (e.g., 1, 2, 2, 3).</t>
+  </si>
+  <si>
+    <t>What is an INSTEAD OF trigger?</t>
+  </si>
+  <si>
+    <t>A trigger used to bypass an INSERT, UPDATE, or DELETE statement to a table or view and execute the statements defined in the trigger instead.</t>
+  </si>
+  <si>
+    <t>What is the purpose of the EXPLAIN command?</t>
+  </si>
+  <si>
+    <t>Used to obtain a description of how the database intends to execute a query, showing information about table scans and index usage.</t>
+  </si>
+  <si>
+    <t>What is a correlated subquery?</t>
+  </si>
+  <si>
+    <t>A subquery that depends on the outer query for its values. It is executed once for every row processed by the outer query.</t>
+  </si>
+  <si>
+    <t>What is the purpose of the SET NOCOUNT ON command?</t>
+  </si>
+  <si>
+    <t>In SQL Server, it stops the message that shows the number of rows affected by a T-SQL statement from being returned as part of the result set (improves performance).</t>
+  </si>
+  <si>
+    <t>Difference between PRIMARY KEY and UNIQUE constraint?</t>
+  </si>
+  <si>
+    <t>Primary key uniquely identifies a record and cannot be NULL. Unique constraint ensures uniqueness but can allow one NULL value (in most DBs).</t>
+  </si>
+  <si>
+    <t>How do you select the last N records?</t>
+  </si>
+  <si>
+    <t>By sorting the result set in DESC order and using the LIMIT N or TOP N clause.</t>
+  </si>
+  <si>
+    <t>What is an autonomous transaction?</t>
+  </si>
+  <si>
+    <t>In PL/SQL, a transaction that is started by another transaction but is independent of it. Changes are committed regardless of the main transaction's outcome.</t>
+  </si>
+  <si>
+    <t>What is the difference between DATE and TIMESTAMP?</t>
+  </si>
+  <si>
+    <t>DATE usually stores year, month, and day. TIMESTAMP stores date and time (often including fractional seconds).</t>
+  </si>
+  <si>
+    <t>What is the NVL function?</t>
+  </si>
+  <si>
+    <t>An Oracle function that lets you substitute a value when a NULL value is encountered.</t>
+  </si>
+  <si>
+    <t>What is a DML trigger?</t>
+  </si>
+  <si>
+    <t>A trigger that fires in response to Data Manipulation Language events (INSERT, UPDATE, DELETE).</t>
+  </si>
+  <si>
+    <t>Difference between CHAR and VARCHAR2 in Oracle?</t>
+  </si>
+  <si>
+    <t>CHAR is fixed-length (padded with spaces). VARCHAR2 is variable-length (no padding).</t>
+  </si>
+  <si>
+    <t>What is the %ROWCOUNT attribute?</t>
+  </si>
+  <si>
+    <t>In PL/SQL, it returns the number of rows affected by the last SQL statement.</t>
+  </si>
+  <si>
+    <t>What is a cursor in SQL?</t>
+  </si>
+  <si>
+    <t>A control structure that enables traversal over the records in a database. It acts as a pointer to a specific row within a query result.</t>
+  </si>
+  <si>
+    <t>Difference between implicit and explicit cursors?</t>
+  </si>
+  <si>
+    <t>Implicit cursors are created by the DB for every SQL DML statement. Explicit cursors are defined by the programmer for queries that return more than one row.</t>
+  </si>
+  <si>
+    <t>What is a sequence in SQL?</t>
+  </si>
+  <si>
+    <t>A user-defined schema-bound object that generates a sequence of numeric values according to a specification.</t>
+  </si>
+  <si>
+    <t>What is the purpose of the GRANT and REVOKE commands?</t>
+  </si>
+  <si>
+    <t>GRANT gives specific permissions to a user to perform tasks. REVOKE takes those permissions back.</t>
+  </si>
+  <si>
+    <t>What is a schema-bound view?</t>
+  </si>
+  <si>
+    <t>A view that is bound to the schema of the underlying tables, preventing changes to the tables that would affect the view definition.</t>
+  </si>
+  <si>
+    <t>What is a 'Phantom Read'?</t>
+  </si>
+  <si>
+    <t>A situation where a transaction reads a set of rows, but then a second transaction inserts a new row that fits the original criteria before the first transaction finishes.</t>
+  </si>
+  <si>
+    <t>What is the difference between a local and global temporary table?</t>
+  </si>
+  <si>
+    <t>In SQL Server, local (#table) is visible only to the current session. Global (##table) is visible to all sessions.</t>
+  </si>
+  <si>
+    <t>What is a lateral join?</t>
+  </si>
+  <si>
+    <t>A join that allows a subquery in the FROM clause to refer to columns of preceding items in the FROM list.</t>
+  </si>
+  <si>
+    <t>What is a natural join?</t>
+  </si>
+  <si>
+    <t>A type of join that automatically joins tables based on columns with the same name and data type in both tables.</t>
+  </si>
+  <si>
+    <t>What is the role of the Parsing Engine in Teradata?</t>
+  </si>
+  <si>
+    <t>It receives SQL requests, optimizes them, creates execution steps, and coordinates the Access Module Processors (AMPs).</t>
+  </si>
+  <si>
+    <t>What is an AMP in Teradata?</t>
+  </si>
+  <si>
+    <t>Access Module Processor; the virtual processor responsible for managing data storage and retrieval in Teradata's parallel architecture.</t>
+  </si>
+  <si>
+    <t>What is skew in Teradata?</t>
+  </si>
+  <si>
+    <t>Uneven distribution of data across AMPs, which can significantly degrade parallel processing performance.</t>
+  </si>
+  <si>
+    <t>What is the BYNET in Teradata?</t>
+  </si>
+  <si>
+    <t>The high-speed communication network that connects the Parsing Engines and AMPs.</t>
+  </si>
+  <si>
+    <t>What is a partitioned primary index (PPI)?</t>
+  </si>
+  <si>
+    <t>A type of primary index in Teradata that physically partitions data on disk to improve performance for range-based queries.</t>
+  </si>
+  <si>
+    <t>What is the difference between FastLoad and MultiLoad?</t>
+  </si>
+  <si>
+    <t>FastLoad is used for loading data into empty tables (very fast). MultiLoad can handle INSERT, UPDATE, and DELETE on populated tables.</t>
+  </si>
+  <si>
+    <t>What is a spool space overflow?</t>
+  </si>
+  <si>
+    <t>An error that occurs when a query requires more temporary storage space than is allocated to the user or system.</t>
+  </si>
+  <si>
+    <t>How does Teradata ensure high availability?</t>
+  </si>
+  <si>
+    <t>Through features like Hot Standby Nodes, Fallback (storing a copy of data on a different AMP), and RAID protection.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -54,7 +1192,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,11 +1200,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -402,9 +1566,4139 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FCA44DC-59A5-4E5B-B422-1D0C0311639D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C375"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="3"/>
+    <col min="2" max="2" width="61" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>104</v>
+      </c>
+      <c r="C54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="3">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>110</v>
+      </c>
+      <c r="C57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>112</v>
+      </c>
+      <c r="C58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="3">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>114</v>
+      </c>
+      <c r="C59" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>116</v>
+      </c>
+      <c r="C60" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="3">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>118</v>
+      </c>
+      <c r="C61" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="3">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>120</v>
+      </c>
+      <c r="C62" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="3">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>122</v>
+      </c>
+      <c r="C63" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="3">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="3">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>126</v>
+      </c>
+      <c r="C65" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="3">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="3">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>130</v>
+      </c>
+      <c r="C67" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="3">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="3">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="3">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="3">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>138</v>
+      </c>
+      <c r="C71" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="3">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>140</v>
+      </c>
+      <c r="C72" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="3">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>142</v>
+      </c>
+      <c r="C73" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="3">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>144</v>
+      </c>
+      <c r="C74" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="3">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>146</v>
+      </c>
+      <c r="C75" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" s="3">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>148</v>
+      </c>
+      <c r="C76" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="3">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>150</v>
+      </c>
+      <c r="C77" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="3">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="3">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>154</v>
+      </c>
+      <c r="C79" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="3">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>156</v>
+      </c>
+      <c r="C80" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" s="3">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>158</v>
+      </c>
+      <c r="C81" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="3">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>160</v>
+      </c>
+      <c r="C82" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="3">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>162</v>
+      </c>
+      <c r="C83" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="3">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>164</v>
+      </c>
+      <c r="C84" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="3">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>166</v>
+      </c>
+      <c r="C85" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="3">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>168</v>
+      </c>
+      <c r="C86" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="3">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="3">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>172</v>
+      </c>
+      <c r="C88" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="3">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="3">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="3">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="3">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" s="3">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="3">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" s="3">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" s="3">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" s="3">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" s="3">
+        <v>97</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" s="3">
+        <v>98</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="3">
+        <v>99</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="3">
+        <v>100</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" s="3">
+        <v>101</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" s="3">
+        <v>102</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" s="3">
+        <v>103</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="3">
+        <v>104</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" s="3">
+        <v>105</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" s="3">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" s="3">
+        <v>107</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="3">
+        <v>108</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" s="3">
+        <v>109</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" s="3">
+        <v>110</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" s="3">
+        <v>111</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="3">
+        <v>112</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="3">
+        <v>113</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="3">
+        <v>114</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" s="3">
+        <v>115</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" s="3">
+        <v>116</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" s="3">
+        <v>117</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" s="3">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" s="3">
+        <v>119</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" s="3">
+        <v>120</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" s="3">
+        <v>121</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" s="3">
+        <v>122</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" s="3">
+        <v>123</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" s="3">
+        <v>124</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" s="3">
+        <v>125</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" s="3">
+        <v>126</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" s="3">
+        <v>127</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" s="3">
+        <v>128</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" s="3">
+        <v>129</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" s="3">
+        <v>130</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" s="3">
+        <v>131</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" s="3">
+        <v>132</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134" s="3">
+        <v>133</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" s="3">
+        <v>134</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136" s="3">
+        <v>135</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137" s="3">
+        <v>136</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" s="3">
+        <v>137</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" s="3">
+        <v>138</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" s="3">
+        <v>139</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" s="3">
+        <v>140</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" s="3">
+        <v>141</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" s="3">
+        <v>142</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" s="3">
+        <v>143</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" s="3">
+        <v>144</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" s="3">
+        <v>145</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" s="3">
+        <v>146</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" s="3">
+        <v>147</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" s="3">
+        <v>148</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" s="3">
+        <v>149</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" s="3">
+        <v>150</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" s="3">
+        <v>151</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" s="3">
+        <v>152</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" s="3">
+        <v>153</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" s="3">
+        <v>154</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" s="3">
+        <v>155</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" s="3">
+        <v>156</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" s="3">
+        <v>157</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" s="3">
+        <v>158</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" s="3">
+        <v>159</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" s="3">
+        <v>160</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" s="3">
+        <v>161</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163" s="3">
+        <v>162</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164" s="3">
+        <v>163</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165" s="3">
+        <v>164</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" s="3">
+        <v>165</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167" s="3">
+        <v>166</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" s="3">
+        <v>167</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" s="3">
+        <v>168</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" s="3">
+        <v>169</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171" s="3">
+        <v>170</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" s="3">
+        <v>171</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" s="3">
+        <v>172</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174" s="3">
+        <v>173</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" s="3">
+        <v>174</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176" s="3">
+        <v>175</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" s="3">
+        <v>176</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178" s="3">
+        <v>177</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" s="3">
+        <v>178</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180" s="3">
+        <v>179</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181" s="3">
+        <v>180</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182" s="3">
+        <v>181</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183" s="3">
+        <v>182</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184" s="3">
+        <v>183</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185" s="3">
+        <v>184</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186" s="3">
+        <v>185</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187" s="3">
+        <v>186</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188" s="3">
+        <v>187</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189" s="3">
+        <v>188</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190" s="3">
+        <v>189</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191" s="3">
+        <v>190</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192" s="3">
+        <v>191</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193" s="3">
+        <v>192</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194" s="3">
+        <v>193</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195" s="3">
+        <v>194</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196" s="3">
+        <v>195</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197" s="3">
+        <v>196</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198" s="3">
+        <v>197</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199" s="3">
+        <v>198</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200" s="3">
+        <v>199</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201" s="3">
+        <v>200</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A202" s="3">
+        <v>201</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203" s="3">
+        <v>202</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204" s="3">
+        <v>203</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205" s="3">
+        <v>204</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206" s="3">
+        <v>205</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207" s="3">
+        <v>206</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208" s="3">
+        <v>207</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209" s="3">
+        <v>208</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210" s="3">
+        <v>209</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211" s="3">
+        <v>210</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" s="3">
+        <v>211</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" s="3">
+        <v>212</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" s="3">
+        <v>213</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" s="3">
+        <v>214</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" s="3">
+        <v>215</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217" s="3">
+        <v>216</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218" s="3">
+        <v>217</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219" s="3">
+        <v>218</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220" s="3">
+        <v>219</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221" s="3">
+        <v>220</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A222" s="3">
+        <v>221</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A223" s="3">
+        <v>222</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A224" s="3">
+        <v>223</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A225" s="3">
+        <v>224</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A226" s="3">
+        <v>225</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A227" s="3">
+        <v>226</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A228" s="3">
+        <v>227</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A229" s="3">
+        <v>228</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A230" s="3">
+        <v>229</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A231" s="3">
+        <v>230</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A232" s="3">
+        <v>231</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A233" s="3">
+        <v>232</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A234" s="3">
+        <v>233</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A235" s="3">
+        <v>234</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A236" s="3">
+        <v>235</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A237" s="3">
+        <v>236</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A238" s="3">
+        <v>237</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A239" s="3">
+        <v>238</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A240" s="3">
+        <v>239</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A241" s="3">
+        <v>240</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A242" s="3">
+        <v>241</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A243" s="3">
+        <v>242</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A244" s="3">
+        <v>243</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A245" s="3">
+        <v>244</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A246" s="3">
+        <v>245</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A247" s="3">
+        <v>246</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A248" s="3">
+        <v>247</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A249" s="3">
+        <v>248</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A250" s="3">
+        <v>249</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A251" s="3">
+        <v>250</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A252" s="3">
+        <v>251</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A253" s="3">
+        <v>252</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A254" s="3">
+        <v>253</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A255" s="3">
+        <v>254</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A256" s="3">
+        <v>255</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A257" s="3">
+        <v>256</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A258" s="3">
+        <v>257</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A259" s="3">
+        <v>258</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A260" s="3">
+        <v>259</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A261" s="3">
+        <v>260</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A262" s="3">
+        <v>261</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A263" s="3">
+        <v>262</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A264" s="3">
+        <v>263</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A265" s="3">
+        <v>264</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A266" s="3">
+        <v>265</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A267" s="3">
+        <v>266</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A268" s="3">
+        <v>267</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A269" s="3">
+        <v>268</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A270" s="3">
+        <v>269</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A271" s="3">
+        <v>270</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A272" s="3">
+        <v>271</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A273" s="3">
+        <v>272</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A274" s="3">
+        <v>273</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A275" s="3">
+        <v>274</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A276" s="3">
+        <v>275</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A277" s="3">
+        <v>276</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A278" s="3">
+        <v>277</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A279" s="3">
+        <v>278</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A280" s="3">
+        <v>279</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A281" s="3">
+        <v>280</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A282" s="3">
+        <v>281</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A283" s="3">
+        <v>282</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A284" s="3">
+        <v>283</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A285" s="3">
+        <v>284</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A286" s="3">
+        <v>285</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A287" s="3">
+        <v>286</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A288" s="3">
+        <v>287</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A289" s="3">
+        <v>288</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A290" s="3">
+        <v>289</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A291" s="3">
+        <v>290</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A292" s="3">
+        <v>291</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A293" s="3">
+        <v>292</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A294" s="3">
+        <v>293</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A295" s="3">
+        <v>294</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A296" s="3">
+        <v>295</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A297" s="3">
+        <v>296</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A298" s="3">
+        <v>297</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A299" s="3">
+        <v>298</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A300" s="3">
+        <v>299</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A301" s="3">
+        <v>300</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A302" s="3">
+        <v>301</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A303" s="3">
+        <v>302</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A304" s="3">
+        <v>303</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A305" s="3">
+        <v>304</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A306" s="3">
+        <v>305</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A307" s="3">
+        <v>306</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A308" s="3">
+        <v>307</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A309" s="3">
+        <v>308</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A310" s="3">
+        <v>309</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C310" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A311" s="3">
+        <v>310</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A312" s="3">
+        <v>311</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A313" s="3">
+        <v>312</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A314" s="3">
+        <v>313</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A315" s="3">
+        <v>314</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A316" s="3">
+        <v>315</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A317" s="3">
+        <v>316</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A318" s="3">
+        <v>317</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A319" s="3">
+        <v>318</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A320" s="3">
+        <v>319</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A321" s="3">
+        <v>320</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A322" s="3">
+        <v>321</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A323" s="3">
+        <v>322</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A324" s="3">
+        <v>323</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C324" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A325" s="3">
+        <v>324</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A326" s="3">
+        <v>325</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A327" s="3">
+        <v>326</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A328" s="3">
+        <v>327</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C328" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A329" s="3">
+        <v>328</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A330" s="3">
+        <v>329</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C330" s="5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A331" s="3">
+        <v>330</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C331" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A332" s="3">
+        <v>331</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C332" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A333" s="3">
+        <v>332</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C333" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A334" s="3">
+        <v>333</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C334" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A335" s="3">
+        <v>334</v>
+      </c>
+      <c r="B335" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C335" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A336" s="3">
+        <v>335</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C336" s="5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A337" s="3">
+        <v>336</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C337" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A338" s="3">
+        <v>337</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C338" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A339" s="3">
+        <v>338</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C339" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A340" s="3">
+        <v>339</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A341" s="3">
+        <v>340</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A342" s="3">
+        <v>341</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="C342" s="5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A343" s="3">
+        <v>342</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C343" s="5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A344" s="3">
+        <v>343</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C344" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A345" s="3">
+        <v>344</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C345" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A346" s="3">
+        <v>345</v>
+      </c>
+      <c r="B346" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="C346" s="5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A347" s="3">
+        <v>346</v>
+      </c>
+      <c r="B347" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C347" s="5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A348" s="3">
+        <v>347</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C348" s="5" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A349" s="3">
+        <v>348</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C349" s="5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A350" s="3">
+        <v>349</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C350" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A351" s="3">
+        <v>350</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A352" s="3">
+        <v>351</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C352" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A353" s="3">
+        <v>352</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C353" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A354" s="3">
+        <v>353</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="C354" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A355" s="3">
+        <v>354</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C355" s="5" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A356" s="3">
+        <v>355</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C356" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A357" s="3">
+        <v>356</v>
+      </c>
+      <c r="B357" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A358" s="3">
+        <v>357</v>
+      </c>
+      <c r="B358" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C358" s="5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A359" s="3">
+        <v>358</v>
+      </c>
+      <c r="B359" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A360" s="3">
+        <v>359</v>
+      </c>
+      <c r="B360" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C360" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A361" s="3">
+        <v>360</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C361" s="5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A362" s="3">
+        <v>361</v>
+      </c>
+      <c r="B362" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C362" s="5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A363" s="3">
+        <v>362</v>
+      </c>
+      <c r="B363" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C363" s="5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A364" s="3">
+        <v>363</v>
+      </c>
+      <c r="B364" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C364" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A365" s="3">
+        <v>364</v>
+      </c>
+      <c r="B365" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="C365" s="5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A366" s="3">
+        <v>365</v>
+      </c>
+      <c r="B366" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="C366" s="5" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A367" s="3">
+        <v>366</v>
+      </c>
+      <c r="B367" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C367" s="5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A368" s="3">
+        <v>367</v>
+      </c>
+      <c r="B368" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C368" s="5" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A369" s="3">
+        <v>368</v>
+      </c>
+      <c r="B369" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="C369" s="5" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A370" s="3">
+        <v>369</v>
+      </c>
+      <c r="B370" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C370" s="5" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A371" s="3">
+        <v>370</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C371" s="5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A372" s="3">
+        <v>371</v>
+      </c>
+      <c r="B372" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C372" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A373" s="3">
+        <v>372</v>
+      </c>
+      <c r="B373" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C373" s="5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A374" s="3">
+        <v>373</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C374" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A375" s="3">
+        <v>374</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C375" s="5" t="s">
+        <v>374</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>